--- a/apps/market-web/i18n.xlsx
+++ b/apps/market-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="454">
   <si>
     <t>key</t>
   </si>
@@ -1283,6 +1283,96 @@
   </si>
   <si>
     <t>Got it</t>
+  </si>
+  <si>
+    <t>notifications.title</t>
+  </si>
+  <si>
+    <t>通知</t>
+  </si>
+  <si>
+    <t>Notifications</t>
+  </si>
+  <si>
+    <t>notifications.empty</t>
+  </si>
+  <si>
+    <t>目前沒有通知</t>
+  </si>
+  <si>
+    <t>No notifications yet</t>
+  </si>
+  <si>
+    <t>notifications.loading</t>
+  </si>
+  <si>
+    <t>載入中…</t>
+  </si>
+  <si>
+    <t>Loading…</t>
+  </si>
+  <si>
+    <t>notifications.markAllRead</t>
+  </si>
+  <si>
+    <t>全部標為已讀</t>
+  </si>
+  <si>
+    <t>Mark all as read</t>
+  </si>
+  <si>
+    <t>notifications.justNow</t>
+  </si>
+  <si>
+    <t>剛剛</t>
+  </si>
+  <si>
+    <t>Just now</t>
+  </si>
+  <si>
+    <t>notifications.minsAgo</t>
+  </si>
+  <si>
+    <t>{n} 分鐘前</t>
+  </si>
+  <si>
+    <t>{n} min ago</t>
+  </si>
+  <si>
+    <t>notifications.hoursAgo</t>
+  </si>
+  <si>
+    <t>{n} 小時前</t>
+  </si>
+  <si>
+    <t>{n} hr ago</t>
+  </si>
+  <si>
+    <t>notifications.daysAgo</t>
+  </si>
+  <si>
+    <t>{n} 天前</t>
+  </si>
+  <si>
+    <t>{n} days ago</t>
+  </si>
+  <si>
+    <t>notifications.catalogPublished</t>
+  </si>
+  <si>
+    <t>{storeName} 上架了新商品「{catalogName}」</t>
+  </si>
+  <si>
+    <t>{storeName} released a new product "{catalogName}"</t>
+  </si>
+  <si>
+    <t>notifications.storeAnnouncement</t>
+  </si>
+  <si>
+    <t>{storeName}：{title}</t>
+  </si>
+  <si>
+    <t>{storeName}: {title}</t>
   </si>
 </sst>
 </file>
@@ -1668,7 +1758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C161"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -3336,6 +3426,116 @@
         <v>423</v>
       </c>
     </row>
+    <row r="152" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/apps/market-web/i18n.xlsx
+++ b/apps/market-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="512">
   <si>
     <t>key</t>
   </si>
@@ -244,10 +244,10 @@
     <t>market.hero.title</t>
   </si>
   <si>
-    <t>發現值得{collect}的{creator}{works}</t>
-  </si>
-  <si>
-    <t>Discover {creator} {works} worth {collect}</t>
+    <t>發現值得{collect}的{rotating}</t>
+  </si>
+  <si>
+    <t>Discover {rotating} worth {collect}</t>
   </si>
   <si>
     <t>market.hero.collect</t>
@@ -259,13 +259,7 @@
     <t>collecting</t>
   </si>
   <si>
-    <t>market.hero.creator</t>
-  </si>
-  <si>
-    <t>creators’</t>
-  </si>
-  <si>
-    <t>market.hero.works</t>
+    <t>market.hero.rotatingWords.0</t>
   </si>
   <si>
     <t>數位作品</t>
@@ -274,6 +268,60 @@
     <t>digital works</t>
   </si>
   <si>
+    <t>market.hero.rotatingWords.1</t>
+  </si>
+  <si>
+    <t>樂譜</t>
+  </si>
+  <si>
+    <t>sheet music</t>
+  </si>
+  <si>
+    <t>market.hero.rotatingWords.2</t>
+  </si>
+  <si>
+    <t>攝影集</t>
+  </si>
+  <si>
+    <t>photo packs</t>
+  </si>
+  <si>
+    <t>market.hero.rotatingWords.3</t>
+  </si>
+  <si>
+    <t>電子書</t>
+  </si>
+  <si>
+    <t>e-books</t>
+  </si>
+  <si>
+    <t>market.hero.stats.works</t>
+  </si>
+  <si>
+    <t>件作品</t>
+  </si>
+  <si>
+    <t>works</t>
+  </si>
+  <si>
+    <t>market.hero.stats.creators</t>
+  </si>
+  <si>
+    <t>位創作者</t>
+  </si>
+  <si>
+    <t>creators</t>
+  </si>
+  <si>
+    <t>market.hero.stats.sales</t>
+  </si>
+  <si>
+    <t>次購買下載</t>
+  </si>
+  <si>
+    <t>downloads</t>
+  </si>
+  <si>
     <t>market.hero.searchPlaceholder</t>
   </si>
   <si>
@@ -344,6 +392,132 @@
   </si>
   <si>
     <t>market.hero.keywords.5</t>
+  </si>
+  <si>
+    <t>market.cats.eyebrow</t>
+  </si>
+  <si>
+    <t>分類導覽</t>
+  </si>
+  <si>
+    <t>Browse by type</t>
+  </si>
+  <si>
+    <t>market.cats.title</t>
+  </si>
+  <si>
+    <t>你想找哪一種創作？</t>
+  </si>
+  <si>
+    <t>What kind of work are you after?</t>
+  </si>
+  <si>
+    <t>market.cats.count</t>
+  </si>
+  <si>
+    <t>{count} 件作品</t>
+  </si>
+  <si>
+    <t>{count} works</t>
+  </si>
+  <si>
+    <t>market.cats.tileAria</t>
+  </si>
+  <si>
+    <t>瀏覽{cat}</t>
+  </si>
+  <si>
+    <t>Browse {cat}</t>
+  </si>
+  <si>
+    <t>market.trending.eyebrow</t>
+  </si>
+  <si>
+    <t>本週脈動</t>
+  </si>
+  <si>
+    <t>This week</t>
+  </si>
+  <si>
+    <t>market.trending.title</t>
+  </si>
+  <si>
+    <t>熱銷排行</t>
+  </si>
+  <si>
+    <t>Top sellers</t>
+  </si>
+  <si>
+    <t>market.trending.sales</t>
+  </si>
+  <si>
+    <t>已售 {count}</t>
+  </si>
+  <si>
+    <t>{count} sold</t>
+  </si>
+  <si>
+    <t>market.creators.eyebrow</t>
+  </si>
+  <si>
+    <t>Creators</t>
+  </si>
+  <si>
+    <t>market.creators.title</t>
+  </si>
+  <si>
+    <t>活躍創作者</t>
+  </si>
+  <si>
+    <t>Creators in the groove</t>
+  </si>
+  <si>
+    <t>market.creators.meta</t>
+  </si>
+  <si>
+    <t>{works} 件作品 · 售出 {sales}</t>
+  </si>
+  <si>
+    <t>{works} works · {sales} sold</t>
+  </si>
+  <si>
+    <t>market.creators.visit</t>
+  </si>
+  <si>
+    <t>逛逛店面</t>
+  </si>
+  <si>
+    <t>Visit store</t>
+  </si>
+  <si>
+    <t>market.ctaBand.title</t>
+  </si>
+  <si>
+    <t>你也在創作嗎？</t>
+  </si>
+  <si>
+    <t>Do you create too?</t>
+  </si>
+  <si>
+    <t>market.ctaBand.sub</t>
+  </si>
+  <si>
+    <t>把樂譜、攝影集與電子書帶到 Open Jam——免月費開店，成功售出才收 3% 手續費。</t>
+  </si>
+  <si>
+    <t>Bring your sheet music, photography, and e-books to Open Jam — no monthly fee, just a 3% cut when a work sells.</t>
+  </si>
+  <si>
+    <t>market.ctaBand.button</t>
+  </si>
+  <si>
+    <t>market.ctaBand.more</t>
+  </si>
+  <si>
+    <t>了解平台如何運作</t>
+  </si>
+  <si>
+    <t>See how the platform works</t>
   </si>
   <si>
     <t>market.featured.eyebrow</t>
@@ -1758,7 +1932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C161"/>
+  <dimension ref="A1:C181"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -2078,260 +2252,260 @@
         <v>82</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>125</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>149</v>
@@ -2397,142 +2571,142 @@
         <v>165</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>167</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="61" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="62" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="64" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="65" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="66" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="68" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="69" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="70" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2543,719 +2717,719 @@
         <v>203</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="72" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="73" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="74" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="75" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="76" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="77" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>95</v>
+        <v>225</v>
       </c>
     </row>
     <row r="79" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="81" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="82" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="83" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>41</v>
+        <v>239</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>42</v>
+        <v>240</v>
       </c>
     </row>
     <row r="84" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>41</v>
+        <v>242</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>42</v>
+        <v>243</v>
       </c>
     </row>
     <row r="85" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>41</v>
+        <v>245</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>42</v>
+        <v>246</v>
       </c>
     </row>
     <row r="86" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="87" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
     </row>
     <row r="88" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="89" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="90" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>250</v>
+        <v>7</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>251</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="93" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="94" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="95" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="96" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="97" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="98" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>275</v>
+        <v>111</v>
       </c>
     </row>
     <row r="99" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>44</v>
+        <v>281</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>45</v>
+        <v>282</v>
       </c>
     </row>
     <row r="100" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="101" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="102" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>50</v>
+        <v>290</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>51</v>
+        <v>291</v>
       </c>
     </row>
     <row r="103" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>285</v>
+        <v>41</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>286</v>
+        <v>42</v>
       </c>
     </row>
     <row r="104" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>288</v>
+        <v>41</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>289</v>
+        <v>42</v>
       </c>
     </row>
     <row r="105" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>291</v>
+        <v>41</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>292</v>
+        <v>42</v>
       </c>
     </row>
     <row r="106" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="107" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="108" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="109" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="110" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="111" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="112" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="113" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="114" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="115" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="116" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="117" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="118" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>48</v>
+        <v>333</v>
       </c>
     </row>
     <row r="119" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>332</v>
+        <v>44</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>333</v>
+        <v>45</v>
       </c>
     </row>
     <row r="120" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="121" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="122" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>341</v>
+        <v>50</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>342</v>
+        <v>51</v>
       </c>
     </row>
     <row r="123" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="C123" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="124" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="C124" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="125" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="126" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="C126" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="127" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="C127" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="128" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="129" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="C129" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="130" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="C130" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="131" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="132" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="133" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="C133" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="134" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="C134" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="135" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="C135" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="136" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>383</v>
@@ -3280,48 +3454,48 @@
         <v>388</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>389</v>
+        <v>48</v>
       </c>
     </row>
     <row r="139" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="C139" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="C140" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="C141" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="142" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>400</v>
@@ -3376,164 +3550,384 @@
         <v>413</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>23</v>
+        <v>414</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>24</v>
+        <v>415</v>
       </c>
     </row>
     <row r="148" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="149" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>26</v>
+        <v>420</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>27</v>
+        <v>421</v>
       </c>
     </row>
     <row r="150" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="151" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="152" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="153" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="154" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="155" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="156" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="157" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="158" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="159" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="160" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="161" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>511</v>
       </c>
     </row>
   </sheetData>

--- a/apps/market-web/i18n.xlsx
+++ b/apps/market-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="514">
   <si>
     <t>key</t>
   </si>
@@ -298,7 +298,7 @@
     <t>market.hero.stats.works</t>
   </si>
   <si>
-    <t>件作品</t>
+    <t>作品</t>
   </si>
   <si>
     <t>works</t>
@@ -307,21 +307,54 @@
     <t>market.hero.stats.creators</t>
   </si>
   <si>
-    <t>位創作者</t>
-  </si>
-  <si>
     <t>creators</t>
   </si>
   <si>
     <t>market.hero.stats.sales</t>
   </si>
   <si>
-    <t>次購買下載</t>
+    <t>次下載</t>
   </si>
   <si>
     <t>downloads</t>
   </si>
   <si>
+    <t>market.hero.cta.explore</t>
+  </si>
+  <si>
+    <t>立即探索</t>
+  </si>
+  <si>
+    <t>Explore now</t>
+  </si>
+  <si>
+    <t>market.hero.cta.hot</t>
+  </si>
+  <si>
+    <t>熱門作品</t>
+  </si>
+  <si>
+    <t>Hot picks</t>
+  </si>
+  <si>
+    <t>market.hero.cta.free</t>
+  </si>
+  <si>
+    <t>免費下載</t>
+  </si>
+  <si>
+    <t>Free downloads</t>
+  </si>
+  <si>
+    <t>market.hero.cta.sell</t>
+  </si>
+  <si>
+    <t>開始販售</t>
+  </si>
+  <si>
+    <t>Start selling</t>
+  </si>
+  <si>
     <t>market.hero.searchPlaceholder</t>
   </si>
   <si>
@@ -340,517 +373,490 @@
     <t>Search the marketplace</t>
   </si>
   <si>
-    <t>market.hero.popularSearch</t>
-  </si>
-  <si>
-    <t>熱門搜尋</t>
+    <t>market.cats.eyebrow</t>
+  </si>
+  <si>
+    <t>分類導覽</t>
+  </si>
+  <si>
+    <t>Browse by type</t>
+  </si>
+  <si>
+    <t>market.cats.title</t>
+  </si>
+  <si>
+    <t>你想找哪一種創作？</t>
+  </si>
+  <si>
+    <t>What kind of work are you after?</t>
+  </si>
+  <si>
+    <t>market.cats.count</t>
+  </si>
+  <si>
+    <t>{count} 件作品</t>
+  </si>
+  <si>
+    <t>{count} works</t>
+  </si>
+  <si>
+    <t>market.cats.tileAria</t>
+  </si>
+  <si>
+    <t>瀏覽{cat}</t>
+  </si>
+  <si>
+    <t>Browse {cat}</t>
+  </si>
+  <si>
+    <t>market.hotBanner.eyebrow</t>
+  </si>
+  <si>
+    <t>本週熱門</t>
+  </si>
+  <si>
+    <t>This week's hottest</t>
+  </si>
+  <si>
+    <t>market.hotBanner.cta</t>
+  </si>
+  <si>
+    <t>查看作品</t>
+  </si>
+  <si>
+    <t>View work</t>
+  </si>
+  <si>
+    <t>market.pulse.eyebrow</t>
+  </si>
+  <si>
+    <t>市集脈動</t>
+  </si>
+  <si>
+    <t>Market pulse</t>
+  </si>
+  <si>
+    <t>market.pulse.title</t>
+  </si>
+  <si>
+    <t>本週市集動態</t>
+  </si>
+  <si>
+    <t>This week at a glance</t>
+  </si>
+  <si>
+    <t>market.trending.title</t>
+  </si>
+  <si>
+    <t>熱銷排行</t>
+  </si>
+  <si>
+    <t>Top sellers</t>
+  </si>
+  <si>
+    <t>market.trending.sales</t>
+  </si>
+  <si>
+    <t>已售 {count}</t>
+  </si>
+  <si>
+    <t>{count} sold</t>
+  </si>
+  <si>
+    <t>market.rated.title</t>
+  </si>
+  <si>
+    <t>評分最高</t>
+  </si>
+  <si>
+    <t>Top rated</t>
+  </si>
+  <si>
+    <t>market.rated.count</t>
+  </si>
+  <si>
+    <t>{count} 則評價</t>
+  </si>
+  <si>
+    <t>{count} reviews</t>
+  </si>
+  <si>
+    <t>market.creators.title</t>
+  </si>
+  <si>
+    <t>人氣創作者</t>
+  </si>
+  <si>
+    <t>Top creators</t>
+  </si>
+  <si>
+    <t>market.creators.works</t>
+  </si>
+  <si>
+    <t>market.creators.sold</t>
+  </si>
+  <si>
+    <t>售出 {count}</t>
+  </si>
+  <si>
+    <t>market.ctaBand.title</t>
+  </si>
+  <si>
+    <t>你也在創作嗎？</t>
+  </si>
+  <si>
+    <t>Do you create too?</t>
+  </si>
+  <si>
+    <t>market.ctaBand.sub</t>
+  </si>
+  <si>
+    <t>把樂譜、攝影集與電子書帶到 Open Jam——免月費開店，成功售出才收 3% 手續費。</t>
+  </si>
+  <si>
+    <t>Bring your sheet music, photography, and e-books to Open Jam — no monthly fee, just a 3% cut when a work sells.</t>
+  </si>
+  <si>
+    <t>market.ctaBand.button</t>
+  </si>
+  <si>
+    <t>market.ctaBand.more</t>
+  </si>
+  <si>
+    <t>了解平台如何運作</t>
+  </si>
+  <si>
+    <t>See how the platform works</t>
+  </si>
+  <si>
+    <t>market.featured.eyebrow</t>
+  </si>
+  <si>
+    <t>精選 · 熱門</t>
+  </si>
+  <si>
+    <t>Featured · Popular</t>
+  </si>
+  <si>
+    <t>market.featured.title</t>
+  </si>
+  <si>
+    <t>精選作品</t>
+  </si>
+  <si>
+    <t>Featured works</t>
+  </si>
+  <si>
+    <t>market.featured.prevAria</t>
+  </si>
+  <si>
+    <t>上一個精選</t>
+  </si>
+  <si>
+    <t>Previous featured</t>
+  </si>
+  <si>
+    <t>market.featured.nextAria</t>
+  </si>
+  <si>
+    <t>下一個精選</t>
+  </si>
+  <si>
+    <t>Next featured</t>
+  </si>
+  <si>
+    <t>market.browse.eyebrow</t>
+  </si>
+  <si>
+    <t>探索市集</t>
+  </si>
+  <si>
+    <t>Explore the marketplace</t>
+  </si>
+  <si>
+    <t>market.browse.title</t>
+  </si>
+  <si>
+    <t>探索所有作品</t>
+  </si>
+  <si>
+    <t>Browse all works</t>
+  </si>
+  <si>
+    <t>market.browse.sub</t>
+  </si>
+  <si>
+    <t>數千件來自獨立創作者的音樂、攝影與電子書，每一件都能立即下載擁有。</t>
+  </si>
+  <si>
+    <t>Thousands of music, photography, and e-book works from independent creators — each ready to download and own instantly.</t>
+  </si>
+  <si>
+    <t>market.browse.allWorks</t>
+  </si>
+  <si>
+    <t>全部作品</t>
+  </si>
+  <si>
+    <t>All works</t>
+  </si>
+  <si>
+    <t>market.browse.count</t>
+  </si>
+  <si>
+    <t>{cat} · 共 {count} 件作品</t>
+  </si>
+  <si>
+    <t>{cat} · {count} works</t>
+  </si>
+  <si>
+    <t>market.browse.sortLabel</t>
+  </si>
+  <si>
+    <t>排序</t>
+  </si>
+  <si>
+    <t>Sort</t>
+  </si>
+  <si>
+    <t>market.browse.sortAria</t>
+  </si>
+  <si>
+    <t>排序方式</t>
+  </si>
+  <si>
+    <t>Sort by</t>
+  </si>
+  <si>
+    <t>market.browse.filter</t>
+  </si>
+  <si>
+    <t>篩選</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>market.browse.categoryGroup</t>
+  </si>
+  <si>
+    <t>分類</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>market.browse.categoryAria</t>
+  </si>
+  <si>
+    <t>作品分類</t>
+  </si>
+  <si>
+    <t>Work category</t>
+  </si>
+  <si>
+    <t>market.browse.priceGroup</t>
+  </si>
+  <si>
+    <t>價格</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>market.browse.priceAria</t>
+  </si>
+  <si>
+    <t>價格區間</t>
+  </si>
+  <si>
+    <t>Price range</t>
+  </si>
+  <si>
+    <t>market.browse.optionCount</t>
+  </si>
+  <si>
+    <t>{label}（{count}）</t>
+  </si>
+  <si>
+    <t>{label} ({count})</t>
+  </si>
+  <si>
+    <t>market.browse.clearAll</t>
+  </si>
+  <si>
+    <t>清除全部篩選</t>
+  </si>
+  <si>
+    <t>Clear all filters</t>
+  </si>
+  <si>
+    <t>market.browse.filtering</t>
+  </si>
+  <si>
+    <t>篩選中</t>
+  </si>
+  <si>
+    <t>Filtering</t>
+  </si>
+  <si>
+    <t>market.browse.clearAllShort</t>
+  </si>
+  <si>
+    <t>清除全部</t>
+  </si>
+  <si>
+    <t>Clear all</t>
+  </si>
+  <si>
+    <t>market.browse.loadMore</t>
+  </si>
+  <si>
+    <t>載入更多</t>
+  </si>
+  <si>
+    <t>Load more</t>
+  </si>
+  <si>
+    <t>market.browse.loadMoreCount</t>
+  </si>
+  <si>
+    <t>（還有 {count} 件）</t>
+  </si>
+  <si>
+    <t>({count} more)</t>
+  </si>
+  <si>
+    <t>market.browse.emptyTitle</t>
+  </si>
+  <si>
+    <t>找不到符合的作品</t>
+  </si>
+  <si>
+    <t>No matching works found</t>
+  </si>
+  <si>
+    <t>market.browse.emptyDesc</t>
+  </si>
+  <si>
+    <t>試著放寬篩選條件或清除搜尋關鍵字。</t>
+  </si>
+  <si>
+    <t>Try loosening the filters or clearing your search keywords.</t>
+  </si>
+  <si>
+    <t>market.sort.popular</t>
+  </si>
+  <si>
+    <t>最熱門</t>
+  </si>
+  <si>
+    <t>Most popular</t>
+  </si>
+  <si>
+    <t>market.sort.newest</t>
+  </si>
+  <si>
+    <t>最新上架</t>
+  </si>
+  <si>
+    <t>Newest</t>
+  </si>
+  <si>
+    <t>market.sort.rating</t>
+  </si>
+  <si>
+    <t>market.sort.priceAsc</t>
+  </si>
+  <si>
+    <t>價格低 → 高</t>
+  </si>
+  <si>
+    <t>Price: low → high</t>
+  </si>
+  <si>
+    <t>market.sort.priceDesc</t>
+  </si>
+  <si>
+    <t>價格高 → 低</t>
+  </si>
+  <si>
+    <t>Price: high → low</t>
+  </si>
+  <si>
+    <t>market.price.all</t>
+  </si>
+  <si>
+    <t>不限</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>market.price.free</t>
+  </si>
+  <si>
+    <t>market.price.low</t>
+  </si>
+  <si>
+    <t>$1–15</t>
+  </si>
+  <si>
+    <t>market.price.mid</t>
+  </si>
+  <si>
+    <t>$16–30</t>
+  </si>
+  <si>
+    <t>market.price.high</t>
+  </si>
+  <si>
+    <t>$30+</t>
+  </si>
+  <si>
+    <t>market.badge.feat</t>
+  </si>
+  <si>
+    <t>精選</t>
+  </si>
+  <si>
+    <t>Featured</t>
+  </si>
+  <si>
+    <t>market.badge.hot</t>
+  </si>
+  <si>
+    <t>熱賣</t>
+  </si>
+  <si>
+    <t>Bestseller</t>
+  </si>
+  <si>
+    <t>market.badge.new</t>
+  </si>
+  <si>
+    <t>新上架</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>card.editorPick</t>
+  </si>
+  <si>
+    <t>編輯精選</t>
+  </si>
+  <si>
+    <t>Editor’s pick</t>
+  </si>
+  <si>
+    <t>card.hot</t>
+  </si>
+  <si>
+    <t>熱門</t>
   </si>
   <si>
     <t>Popular</t>
-  </si>
-  <si>
-    <t>market.hero.keywords.0</t>
-  </si>
-  <si>
-    <t>爵士</t>
-  </si>
-  <si>
-    <t>Jazz</t>
-  </si>
-  <si>
-    <t>market.hero.keywords.1</t>
-  </si>
-  <si>
-    <t>京都</t>
-  </si>
-  <si>
-    <t>Kyoto</t>
-  </si>
-  <si>
-    <t>market.hero.keywords.2</t>
-  </si>
-  <si>
-    <t>鋼琴</t>
-  </si>
-  <si>
-    <t>Piano</t>
-  </si>
-  <si>
-    <t>market.hero.keywords.3</t>
-  </si>
-  <si>
-    <t>Notion</t>
-  </si>
-  <si>
-    <t>market.hero.keywords.4</t>
-  </si>
-  <si>
-    <t>街拍</t>
-  </si>
-  <si>
-    <t>Street</t>
-  </si>
-  <si>
-    <t>market.hero.keywords.5</t>
-  </si>
-  <si>
-    <t>market.cats.eyebrow</t>
-  </si>
-  <si>
-    <t>分類導覽</t>
-  </si>
-  <si>
-    <t>Browse by type</t>
-  </si>
-  <si>
-    <t>market.cats.title</t>
-  </si>
-  <si>
-    <t>你想找哪一種創作？</t>
-  </si>
-  <si>
-    <t>What kind of work are you after?</t>
-  </si>
-  <si>
-    <t>market.cats.count</t>
-  </si>
-  <si>
-    <t>{count} 件作品</t>
-  </si>
-  <si>
-    <t>{count} works</t>
-  </si>
-  <si>
-    <t>market.cats.tileAria</t>
-  </si>
-  <si>
-    <t>瀏覽{cat}</t>
-  </si>
-  <si>
-    <t>Browse {cat}</t>
-  </si>
-  <si>
-    <t>market.trending.eyebrow</t>
-  </si>
-  <si>
-    <t>本週脈動</t>
-  </si>
-  <si>
-    <t>This week</t>
-  </si>
-  <si>
-    <t>market.trending.title</t>
-  </si>
-  <si>
-    <t>熱銷排行</t>
-  </si>
-  <si>
-    <t>Top sellers</t>
-  </si>
-  <si>
-    <t>market.trending.sales</t>
-  </si>
-  <si>
-    <t>已售 {count}</t>
-  </si>
-  <si>
-    <t>{count} sold</t>
-  </si>
-  <si>
-    <t>market.creators.eyebrow</t>
-  </si>
-  <si>
-    <t>Creators</t>
-  </si>
-  <si>
-    <t>market.creators.title</t>
-  </si>
-  <si>
-    <t>活躍創作者</t>
-  </si>
-  <si>
-    <t>Creators in the groove</t>
-  </si>
-  <si>
-    <t>market.creators.meta</t>
-  </si>
-  <si>
-    <t>{works} 件作品 · 售出 {sales}</t>
-  </si>
-  <si>
-    <t>{works} works · {sales} sold</t>
-  </si>
-  <si>
-    <t>market.creators.visit</t>
-  </si>
-  <si>
-    <t>逛逛店面</t>
-  </si>
-  <si>
-    <t>Visit store</t>
-  </si>
-  <si>
-    <t>market.ctaBand.title</t>
-  </si>
-  <si>
-    <t>你也在創作嗎？</t>
-  </si>
-  <si>
-    <t>Do you create too?</t>
-  </si>
-  <si>
-    <t>market.ctaBand.sub</t>
-  </si>
-  <si>
-    <t>把樂譜、攝影集與電子書帶到 Open Jam——免月費開店，成功售出才收 3% 手續費。</t>
-  </si>
-  <si>
-    <t>Bring your sheet music, photography, and e-books to Open Jam — no monthly fee, just a 3% cut when a work sells.</t>
-  </si>
-  <si>
-    <t>market.ctaBand.button</t>
-  </si>
-  <si>
-    <t>market.ctaBand.more</t>
-  </si>
-  <si>
-    <t>了解平台如何運作</t>
-  </si>
-  <si>
-    <t>See how the platform works</t>
-  </si>
-  <si>
-    <t>market.featured.eyebrow</t>
-  </si>
-  <si>
-    <t>精選 · 熱門</t>
-  </si>
-  <si>
-    <t>Featured · Popular</t>
-  </si>
-  <si>
-    <t>market.featured.title</t>
-  </si>
-  <si>
-    <t>精選作品</t>
-  </si>
-  <si>
-    <t>Featured works</t>
-  </si>
-  <si>
-    <t>market.featured.prevAria</t>
-  </si>
-  <si>
-    <t>上一個精選</t>
-  </si>
-  <si>
-    <t>Previous featured</t>
-  </si>
-  <si>
-    <t>market.featured.nextAria</t>
-  </si>
-  <si>
-    <t>下一個精選</t>
-  </si>
-  <si>
-    <t>Next featured</t>
-  </si>
-  <si>
-    <t>market.browse.eyebrow</t>
-  </si>
-  <si>
-    <t>探索市集</t>
-  </si>
-  <si>
-    <t>Explore the marketplace</t>
-  </si>
-  <si>
-    <t>market.browse.title</t>
-  </si>
-  <si>
-    <t>探索所有作品</t>
-  </si>
-  <si>
-    <t>Browse all works</t>
-  </si>
-  <si>
-    <t>market.browse.sub</t>
-  </si>
-  <si>
-    <t>數千件來自獨立創作者的音樂、攝影與電子書，每一件都能立即下載擁有。</t>
-  </si>
-  <si>
-    <t>Thousands of music, photography, and e-book works from independent creators — each ready to download and own instantly.</t>
-  </si>
-  <si>
-    <t>market.browse.allWorks</t>
-  </si>
-  <si>
-    <t>全部作品</t>
-  </si>
-  <si>
-    <t>All works</t>
-  </si>
-  <si>
-    <t>market.browse.count</t>
-  </si>
-  <si>
-    <t>{cat} · 共 {count} 件作品</t>
-  </si>
-  <si>
-    <t>{cat} · {count} works</t>
-  </si>
-  <si>
-    <t>market.browse.sortLabel</t>
-  </si>
-  <si>
-    <t>排序</t>
-  </si>
-  <si>
-    <t>Sort</t>
-  </si>
-  <si>
-    <t>market.browse.sortAria</t>
-  </si>
-  <si>
-    <t>排序方式</t>
-  </si>
-  <si>
-    <t>Sort by</t>
-  </si>
-  <si>
-    <t>market.browse.filter</t>
-  </si>
-  <si>
-    <t>篩選</t>
-  </si>
-  <si>
-    <t>Filter</t>
-  </si>
-  <si>
-    <t>market.browse.categoryGroup</t>
-  </si>
-  <si>
-    <t>分類</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>market.browse.categoryAria</t>
-  </si>
-  <si>
-    <t>作品分類</t>
-  </si>
-  <si>
-    <t>Work category</t>
-  </si>
-  <si>
-    <t>market.browse.priceGroup</t>
-  </si>
-  <si>
-    <t>價格</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>market.browse.priceAria</t>
-  </si>
-  <si>
-    <t>價格區間</t>
-  </si>
-  <si>
-    <t>Price range</t>
-  </si>
-  <si>
-    <t>market.browse.optionCount</t>
-  </si>
-  <si>
-    <t>{label}（{count}）</t>
-  </si>
-  <si>
-    <t>{label} ({count})</t>
-  </si>
-  <si>
-    <t>market.browse.clearAll</t>
-  </si>
-  <si>
-    <t>清除全部篩選</t>
-  </si>
-  <si>
-    <t>Clear all filters</t>
-  </si>
-  <si>
-    <t>market.browse.filtering</t>
-  </si>
-  <si>
-    <t>篩選中</t>
-  </si>
-  <si>
-    <t>Filtering</t>
-  </si>
-  <si>
-    <t>market.browse.clearAllShort</t>
-  </si>
-  <si>
-    <t>清除全部</t>
-  </si>
-  <si>
-    <t>Clear all</t>
-  </si>
-  <si>
-    <t>market.browse.loadMore</t>
-  </si>
-  <si>
-    <t>載入更多</t>
-  </si>
-  <si>
-    <t>Load more</t>
-  </si>
-  <si>
-    <t>market.browse.loadMoreCount</t>
-  </si>
-  <si>
-    <t>（還有 {count} 件）</t>
-  </si>
-  <si>
-    <t>({count} more)</t>
-  </si>
-  <si>
-    <t>market.browse.emptyTitle</t>
-  </si>
-  <si>
-    <t>找不到符合的作品</t>
-  </si>
-  <si>
-    <t>No matching works found</t>
-  </si>
-  <si>
-    <t>market.browse.emptyDesc</t>
-  </si>
-  <si>
-    <t>試著放寬篩選條件或清除搜尋關鍵字。</t>
-  </si>
-  <si>
-    <t>Try loosening the filters or clearing your search keywords.</t>
-  </si>
-  <si>
-    <t>market.sort.popular</t>
-  </si>
-  <si>
-    <t>最熱門</t>
-  </si>
-  <si>
-    <t>Most popular</t>
-  </si>
-  <si>
-    <t>market.sort.newest</t>
-  </si>
-  <si>
-    <t>最新上架</t>
-  </si>
-  <si>
-    <t>Newest</t>
-  </si>
-  <si>
-    <t>market.sort.rating</t>
-  </si>
-  <si>
-    <t>評分最高</t>
-  </si>
-  <si>
-    <t>Top rated</t>
-  </si>
-  <si>
-    <t>market.sort.priceAsc</t>
-  </si>
-  <si>
-    <t>價格低 → 高</t>
-  </si>
-  <si>
-    <t>Price: low → high</t>
-  </si>
-  <si>
-    <t>market.sort.priceDesc</t>
-  </si>
-  <si>
-    <t>價格高 → 低</t>
-  </si>
-  <si>
-    <t>Price: high → low</t>
-  </si>
-  <si>
-    <t>market.price.all</t>
-  </si>
-  <si>
-    <t>不限</t>
-  </si>
-  <si>
-    <t>Any</t>
-  </si>
-  <si>
-    <t>market.price.free</t>
-  </si>
-  <si>
-    <t>market.price.low</t>
-  </si>
-  <si>
-    <t>$1–15</t>
-  </si>
-  <si>
-    <t>market.price.mid</t>
-  </si>
-  <si>
-    <t>$16–30</t>
-  </si>
-  <si>
-    <t>market.price.high</t>
-  </si>
-  <si>
-    <t>$30+</t>
-  </si>
-  <si>
-    <t>market.badge.feat</t>
-  </si>
-  <si>
-    <t>精選</t>
-  </si>
-  <si>
-    <t>Featured</t>
-  </si>
-  <si>
-    <t>market.badge.hot</t>
-  </si>
-  <si>
-    <t>熱賣</t>
-  </si>
-  <si>
-    <t>Bestseller</t>
-  </si>
-  <si>
-    <t>market.badge.new</t>
-  </si>
-  <si>
-    <t>新上架</t>
-  </si>
-  <si>
-    <t>New</t>
-  </si>
-  <si>
-    <t>card.editorPick</t>
-  </si>
-  <si>
-    <t>編輯精選</t>
-  </si>
-  <si>
-    <t>Editor’s pick</t>
-  </si>
-  <si>
-    <t>card.hot</t>
-  </si>
-  <si>
-    <t>熱門</t>
   </si>
   <si>
     <t>collage.card1</t>
@@ -1932,7 +1938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C181"/>
+  <dimension ref="A1:C182"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -2307,95 +2313,95 @@
         <v>97</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>122</v>
@@ -2417,142 +2423,142 @@
         <v>126</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2571,21 +2577,21 @@
         <v>165</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>45</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>167</v>
+        <v>44</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>168</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2890,43 +2896,43 @@
         <v>250</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>251</v>
+        <v>151</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>252</v>
+        <v>152</v>
       </c>
     </row>
     <row r="88" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="89" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="90" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2934,147 +2940,147 @@
         <v>260</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>261</v>
+        <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>261</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="C92" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="93" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="C93" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="C94" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="95" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="96" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="97" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="98" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="99" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="C99" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="100" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C100" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="101" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C101" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="102" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="C102" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="103" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="C103" s="2" t="s">
-        <v>42</v>
+        <v>293</v>
       </c>
     </row>
     <row r="104" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>41</v>
@@ -3085,7 +3091,7 @@
     </row>
     <row r="105" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>41</v>
@@ -3096,365 +3102,365 @@
     </row>
     <row r="106" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>297</v>
+        <v>42</v>
       </c>
     </row>
     <row r="107" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="C107" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="108" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="109" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="C109" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="110" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C110" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="111" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C111" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="112" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C112" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="113" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="114" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="115" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="C115" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="116" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="117" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="C117" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="118" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="C118" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="119" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="C119" s="2" t="s">
-        <v>45</v>
+        <v>335</v>
       </c>
     </row>
     <row r="120" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>336</v>
+        <v>44</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>337</v>
+        <v>45</v>
       </c>
     </row>
     <row r="121" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="C121" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="122" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C122" s="2" t="s">
-        <v>51</v>
+        <v>342</v>
       </c>
     </row>
     <row r="123" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>343</v>
+        <v>50</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>344</v>
+        <v>51</v>
       </c>
     </row>
     <row r="124" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="C124" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="125" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="126" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="C126" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="127" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="C127" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="128" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="129" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="C129" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="130" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="C130" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="131" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="132" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="133" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="C133" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="134" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="C134" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="135" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="C135" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="136" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="C136" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="137" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="C137" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="138" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="139" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3465,191 +3471,191 @@
         <v>390</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>391</v>
+        <v>48</v>
       </c>
     </row>
     <row r="140" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="C140" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="141" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="C141" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="142" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="C142" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="143" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="C143" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="144" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="C144" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="145" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="C145" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B146" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="C146" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="C147" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="148" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="C148" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="149" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="C149" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="150" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="C150" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="151" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C151" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="152" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="C152" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="153" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="C153" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="154" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="C154" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="155" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="C155" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="156" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B156" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>441</v>
@@ -3663,59 +3669,59 @@
         <v>443</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="158" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="C158" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="159" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B159" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="C159" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="160" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B160" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B160" s="2" t="s">
+      <c r="C160" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="161" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B161" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="C161" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="162" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B162" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>458</v>
@@ -3729,205 +3735,216 @@
         <v>460</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="164" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="C164" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="165" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="C165" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="166" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B166" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="C166" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="167" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B167" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="C167" s="2" t="s">
-        <v>24</v>
+        <v>472</v>
       </c>
     </row>
     <row r="168" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>473</v>
+        <v>23</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>474</v>
+        <v>24</v>
       </c>
     </row>
     <row r="169" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C169" s="2" t="s">
-        <v>27</v>
+        <v>476</v>
       </c>
     </row>
     <row r="170" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>477</v>
+        <v>26</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>478</v>
+        <v>27</v>
       </c>
     </row>
     <row r="171" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B171" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="C171" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="172" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B172" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="C172" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="173" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B173" s="2" t="s">
+      <c r="C173" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="174" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B174" s="2" t="s">
+      <c r="C174" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="175" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B175" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B175" s="2" t="s">
+      <c r="C175" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="176" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B176" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="B176" s="2" t="s">
+      <c r="C176" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="177" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B177" s="2" t="s">
+      <c r="C177" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="178" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B178" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="B178" s="2" t="s">
+      <c r="C178" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="179" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B179" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="C179" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="180" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B180" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="C180" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="181" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B181" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="C181" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="C181" s="2" t="s">
+    </row>
+    <row r="182" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
         <v>511</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>513</v>
       </c>
     </row>
   </sheetData>
